--- a/sample1.xlsx
+++ b/sample1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="241">
   <si>
     <t>Basic Details</t>
   </si>
@@ -359,6 +359,12 @@
     <t>Trade Name</t>
   </si>
   <si>
+    <t>06**********1ZR</t>
+  </si>
+  <si>
+    <t>SH************TED</t>
+  </si>
+  <si>
     <t>ITC received from Inter State cancelled/bogus dealers (Lakhs) (NGTP Cases): **Note: Data is indicative and not exhaustive due to limited PAN-India GSTIN details and incomplete GSTR-2A/2B data; and should be used for reference only.</t>
   </si>
   <si>
@@ -368,6 +374,9 @@
     <t>NGTP Trade/Legal Name</t>
   </si>
   <si>
+    <t>22***********1ZO</t>
+  </si>
+  <si>
     <t>EWB Top 10 HSN wise Sale</t>
   </si>
   <si>
@@ -398,9 +407,6 @@
     <t>Total Sale Amount</t>
   </si>
   <si>
-    <t>22***********1ZO</t>
-  </si>
-  <si>
     <t>6205</t>
   </si>
   <si>
@@ -581,9 +587,6 @@
     <t>30.98</t>
   </si>
   <si>
-    <t>06**********1ZR</t>
-  </si>
-  <si>
     <t>25.14</t>
   </si>
   <si>
@@ -639,9 +642,6 @@
   </si>
   <si>
     <t>22***********2ZJ</t>
-  </si>
-  <si>
-    <t>SH************TED</t>
   </si>
   <si>
     <t>43.47</t>
@@ -1948,7 +1948,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49" style="1" customWidth="1"/>
+    <col min="2" max="2" width="59.2857142857143" style="1" customWidth="1"/>
     <col min="3" max="3" width="43.8571428571429" style="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" customWidth="1"/>
     <col min="5" max="5" width="38" style="1" customWidth="1"/>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:2">
       <c r="A91" s="4">
-        <v>0</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="B91" s="4">
+        <v>10.36</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1"/>
@@ -3070,11 +3070,21 @@
         <v>107</v>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1"/>
+    <row r="96" ht="20" customHeight="1" spans="1:3">
+      <c r="A96" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C96" s="4">
+        <v>10.36</v>
+      </c>
+    </row>
     <row r="97" ht="20" customHeight="1"/>
     <row r="98" ht="20" customHeight="1" spans="1:1">
       <c r="A98" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:5">
@@ -3082,10 +3092,10 @@
         <v>92</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>33</v>
@@ -3094,51 +3104,67 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1" spans="1:5">
+      <c r="A100" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E100" s="4">
+        <v>10.36</v>
+      </c>
+    </row>
     <row r="101" ht="20" customHeight="1"/>
     <row r="102" ht="20" customHeight="1" spans="1:1">
       <c r="A102" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:9">
       <c r="A103" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:9">
       <c r="A104" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D104" s="4">
         <v>6083102.67000001</v>
@@ -3161,13 +3187,13 @@
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:9">
       <c r="A105" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D105" s="4">
         <v>3557860.54</v>
@@ -3190,13 +3216,13 @@
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:9">
       <c r="A106" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D106" s="4">
         <v>5750749.12999999</v>
@@ -3219,13 +3245,13 @@
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:9">
       <c r="A107" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D107" s="4">
         <v>1520160.54</v>
@@ -3248,13 +3274,13 @@
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:9">
       <c r="A108" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D108" s="4">
         <v>810768.19</v>
@@ -3277,13 +3303,13 @@
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:9">
       <c r="A109" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D109" s="4">
         <v>221253.11</v>
@@ -3306,13 +3332,13 @@
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:9">
       <c r="A110" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D110" s="4">
         <v>872494.5</v>
@@ -3335,13 +3361,13 @@
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:9">
       <c r="A111" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D111" s="4">
         <v>1196417.61</v>
@@ -3364,13 +3390,13 @@
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:9">
       <c r="A112" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D112" s="4">
         <v>744311.31</v>
@@ -3393,13 +3419,13 @@
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:9">
       <c r="A113" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D113" s="4">
         <v>0</v>
@@ -3424,47 +3450,47 @@
     <row r="115" ht="20" customHeight="1"/>
     <row r="116" ht="20" customHeight="1" spans="1:1">
       <c r="A116" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:9">
       <c r="A117" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:9">
       <c r="A118" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D118" s="4">
         <v>19858634.24</v>
@@ -3487,13 +3513,13 @@
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:9">
       <c r="A119" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D119" s="4">
         <v>12140208.78</v>
@@ -3516,13 +3542,13 @@
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:9">
       <c r="A120" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D120" s="4">
         <v>13312594.55</v>
@@ -3545,13 +3571,13 @@
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:9">
       <c r="A121" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D121" s="4">
         <v>3689792.45</v>
@@ -3574,13 +3600,13 @@
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:9">
       <c r="A122" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D122" s="4">
         <v>3017719.9</v>
@@ -3603,13 +3629,13 @@
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:9">
       <c r="A123" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D123" s="4">
         <v>2088537.98</v>
@@ -3632,13 +3658,13 @@
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:9">
       <c r="A124" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D124" s="4">
         <v>1390782.29</v>
@@ -3661,13 +3687,13 @@
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:9">
       <c r="A125" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D125" s="4">
         <v>1276519.95</v>
@@ -3690,13 +3716,13 @@
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:9">
       <c r="A126" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D126" s="4">
         <v>552835.85</v>
@@ -3719,13 +3745,13 @@
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:9">
       <c r="A127" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D127" s="4">
         <v>0</v>
@@ -3750,182 +3776,182 @@
     <row r="129" ht="20" customHeight="1"/>
     <row r="130" ht="20" customHeight="1" spans="1:1">
       <c r="A130" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:4">
       <c r="A131" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:4">
       <c r="A132" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:4">
       <c r="A133" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="D133" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:4">
       <c r="A134" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:4">
       <c r="A135" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:4">
       <c r="A136" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:4">
       <c r="A137" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:4">
       <c r="A138" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:4">
       <c r="A139" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:4">
       <c r="A140" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:4">
       <c r="A141" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:4">
       <c r="A142" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B142" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="D142" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1"/>
     <row r="144" ht="20" customHeight="1"/>
     <row r="145" ht="20" customHeight="1" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:7">
@@ -3933,36 +3959,36 @@
         <v>92</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:7">
       <c r="A147" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>31</v>
@@ -3971,21 +3997,21 @@
         <v>31</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:7">
       <c r="A148" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>31</v>
@@ -3994,21 +4020,21 @@
         <v>31</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:7">
       <c r="A149" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>31</v>
@@ -4017,21 +4043,21 @@
         <v>31</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:7">
       <c r="A150" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>31</v>
@@ -4040,21 +4066,21 @@
         <v>31</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:7">
       <c r="A151" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>31</v>
@@ -4063,21 +4089,21 @@
         <v>31</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:7">
       <c r="A152" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>31</v>
@@ -4086,21 +4112,21 @@
         <v>31</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:7">
       <c r="A153" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>31</v>
@@ -4109,21 +4135,21 @@
         <v>31</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:7">
       <c r="A154" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>31</v>
@@ -4132,21 +4158,21 @@
         <v>31</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:7">
       <c r="A155" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>31</v>
@@ -4155,21 +4181,21 @@
         <v>31</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:7">
       <c r="A156" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>31</v>
@@ -4178,14 +4204,14 @@
         <v>31</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1"/>
     <row r="158" ht="20" customHeight="1"/>
     <row r="159" ht="20" customHeight="1" spans="1:1">
       <c r="A159" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:7">
@@ -4193,42 +4219,42 @@
         <v>92</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:7">
       <c r="A161" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>205</v>
@@ -4236,13 +4262,13 @@
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:7">
       <c r="A162" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>206</v>
@@ -4259,13 +4285,13 @@
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:7">
       <c r="A163" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>206</v>
@@ -4282,22 +4308,22 @@
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:7">
       <c r="A164" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>209</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>210</v>
@@ -4305,13 +4331,13 @@
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:7">
       <c r="A165" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>211</v>
@@ -4328,22 +4354,22 @@
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:7">
       <c r="A166" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>213</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>214</v>
@@ -4351,22 +4377,22 @@
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:7">
       <c r="A167" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>215</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>216</v>
@@ -4374,22 +4400,22 @@
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:7">
       <c r="A168" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>217</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>218</v>
@@ -4397,22 +4423,22 @@
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:7">
       <c r="A169" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>219</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>220</v>
@@ -4420,22 +4446,22 @@
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:7">
       <c r="A170" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>222</v>
@@ -4895,7 +4921,7 @@
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:5">
       <c r="A207" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>39</v>
@@ -4912,7 +4938,7 @@
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:5">
       <c r="A208" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>40</v>
@@ -4929,7 +4955,7 @@
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:5">
       <c r="A209" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>42</v>
@@ -4946,7 +4972,7 @@
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:5">
       <c r="A210" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>44</v>
@@ -4963,7 +4989,7 @@
     </row>
     <row r="211" ht="20" customHeight="1" spans="1:5">
       <c r="A211" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>46</v>
